--- a/9_asistencia_evaluacion/respuestas_prueba_diagnostica_limpia.xlsx
+++ b/9_asistencia_evaluacion/respuestas_prueba_diagnostica_limpia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\extension\camino-udea\9_asistencia_evaluacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CC3720-4CF7-4796-AEB5-970ED290AA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFF67EA-5A60-49EB-A9F6-8FDD4FF0737D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,7 +272,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -305,7 +305,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -611,6 +611,7 @@
   <dimension ref="A1:AO36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="28.77734375" customWidth="1"/>
     <col min="3" max="3" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
